--- a/Result/profitability/1810.xlsx
+++ b/Result/profitability/1810.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.03</v>
       </c>
       <c r="M2" t="n">
-        <v>0.48625</v>
+        <v>0.46375</v>
       </c>
       <c r="N2" t="n">
-        <v>24.65625</v>
+        <v>24.57875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.13</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4825</v>
+        <v>0.4787500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>24.855</v>
+        <v>24.94</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4725</v>
+        <v>0.48125</v>
       </c>
       <c r="N4" t="n">
-        <v>25.37875</v>
+        <v>25.4825</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.42</v>
       </c>
       <c r="M5" t="n">
-        <v>0.43125</v>
+        <v>0.41625</v>
       </c>
       <c r="N5" t="n">
-        <v>25.67</v>
+        <v>25.5125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.27</v>
       </c>
       <c r="M6" t="n">
-        <v>0.385</v>
+        <v>0.37875</v>
       </c>
       <c r="N6" t="n">
-        <v>24.98875</v>
+        <v>24.93125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.04</v>
       </c>
       <c r="M7" t="n">
-        <v>0.37625</v>
+        <v>0.3725</v>
       </c>
       <c r="N7" t="n">
-        <v>24.75</v>
+        <v>24.66625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.19</v>
       </c>
       <c r="M8" t="n">
-        <v>0.35125</v>
+        <v>-0.10625</v>
       </c>
       <c r="N8" t="n">
-        <v>24.525</v>
+        <v>25.53</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9842,6 +9842,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1810</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1147</v>
+      </c>
+      <c r="D75" t="n">
+        <v>855</v>
+      </c>
+      <c r="E75" t="n">
+        <v>291</v>
+      </c>
+      <c r="F75" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-28</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-2.43%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>33</v>
+      </c>
+      <c r="J75" t="n">
+        <v>6</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="N75" t="n">
+        <v>24.5825</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-3.66</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.005494505494505</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.4631336405529953</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.260000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.04726181545386354</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
